--- a/inputs/adam_spec_CDSC-ALZ-201.xlsx
+++ b/inputs/adam_spec_CDSC-ALZ-201.xlsx
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Study Identifier</t>
+          <t/>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Unique Subject Identifier</t>
+          <t/>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Safety Population Flag</t>
+          <t/>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Planned Treatment</t>
+          <t/>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Actual Treatment</t>
+          <t/>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sequence Number</t>
+          <t/>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reported Name of Drug, Med, or Therapy</t>
+          <t/>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="E8">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Standardized Medication Name</t>
+          <t/>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Medication Class</t>
+          <t/>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indication</t>
+          <t/>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Start Date/Time of Medication</t>
+          <t/>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>End Date/Time of Medication</t>
+          <t/>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Analysis Start Date</t>
+          <t/>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Analysis Start Relative Day</t>
+          <t/>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Analysis End Date</t>
+          <t/>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>On Treatment Record Flag</t>
+          <t/>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1st Occurrence of Preferred Term Flag</t>
+          <t/>
         </is>
       </c>
       <c r="D18" t="inlineStr">
